--- a/documentation/leetcode/leetcode.xlsx
+++ b/documentation/leetcode/leetcode.xlsx
@@ -9,10 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="28760" windowHeight="17300" tabRatio="500"/>
+    <workbookView xWindow="-180" yWindow="4720" windowWidth="28760" windowHeight="17300" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="links" sheetId="2" r:id="rId1"/>
+    <sheet name="problems" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="150000" concurrentCalc="0"/>
   <extLst>
@@ -26,12 +27,192 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="54">
+  <si>
+    <t>1. Two Sum</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>2. Add Two Numbers</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>3. Longest Substring Without Repeating Characters</t>
+  </si>
+  <si>
+    <t>4. Median of Two Sorted Arrays</t>
+  </si>
+  <si>
+    <t>Hard</t>
+  </si>
+  <si>
+    <t>5. Longest Palindromic Substring</t>
+  </si>
+  <si>
+    <t>6. Zigzag Conversion</t>
+  </si>
+  <si>
+    <t>7. Reverse Integer</t>
+  </si>
+  <si>
+    <t>8. String to Integer (atoi)</t>
+  </si>
+  <si>
+    <t>9. Palindrome Number</t>
+  </si>
+  <si>
+    <t>10. Regular Expression Matching</t>
+  </si>
+  <si>
+    <t>11. Container With Most Water</t>
+  </si>
+  <si>
+    <t>12. Integer to Roman</t>
+  </si>
+  <si>
+    <t>13. Roman to Integer</t>
+  </si>
+  <si>
+    <t>14. Longest Common Prefix</t>
+  </si>
+  <si>
+    <t>15. 3Sum</t>
+  </si>
+  <si>
+    <t>16. 3Sum Closest</t>
+  </si>
+  <si>
+    <t>17. Letter Combinations of a Phone Number</t>
+  </si>
+  <si>
+    <t>18. 4Sum</t>
+  </si>
+  <si>
+    <t>19. Remove Nth Node From End of List</t>
+  </si>
+  <si>
+    <t>20. Valid Parentheses</t>
+  </si>
+  <si>
+    <t>21. Merge Two Sorted Lists</t>
+  </si>
+  <si>
+    <t>22. Generate Parentheses</t>
+  </si>
+  <si>
+    <t>23. Merge k Sorted Lists</t>
+  </si>
+  <si>
+    <t>24. Swap Nodes in Pairs</t>
+  </si>
+  <si>
+    <t>25. Reverse Nodes in k-Group</t>
+  </si>
+  <si>
+    <t>26. Remove Duplicates from Sorted Array</t>
+  </si>
+  <si>
+    <t>27. Remove Element</t>
+  </si>
+  <si>
+    <t>28. Find the Index of the First Occurrence in a String</t>
+  </si>
+  <si>
+    <t>29. Divide Two Integers</t>
+  </si>
+  <si>
+    <t>30. Substring with Concatenation of All Words</t>
+  </si>
+  <si>
+    <t>31. Next Permutation</t>
+  </si>
+  <si>
+    <t>32. Longest Valid Parentheses</t>
+  </si>
+  <si>
+    <t>33. Search in Rotated Sorted Array</t>
+  </si>
+  <si>
+    <t>34. Find First and Last Position of Element in Sorted Array</t>
+  </si>
+  <si>
+    <t>35. Search Insert Position</t>
+  </si>
+  <si>
+    <t>36. Valid Sudoku</t>
+  </si>
+  <si>
+    <t>37. Sudoku Solver</t>
+  </si>
+  <si>
+    <t>38. Count and Say</t>
+  </si>
+  <si>
+    <t>39. Combination Sum</t>
+  </si>
+  <si>
+    <t>40. Combination Sum II</t>
+  </si>
+  <si>
+    <t>41. First Missing Positive</t>
+  </si>
+  <si>
+    <t>42. Trapping Rain Water</t>
+  </si>
+  <si>
+    <t>43. Multiply Strings</t>
+  </si>
+  <si>
+    <t>44. Wildcard Matching</t>
+  </si>
+  <si>
+    <t>45. Jump Game II</t>
+  </si>
+  <si>
+    <t>46. Permutations</t>
+  </si>
+  <si>
+    <t>47. Permutations II</t>
+  </si>
+  <si>
+    <t>48. Rotate Image</t>
+  </si>
+  <si>
+    <t>49. Group Anagrams</t>
+  </si>
+  <si>
+    <t>50. Pow(x, n)</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problemset/</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Helvetica"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -54,13 +235,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -336,9 +522,493 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="48.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:B53"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="49.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
+        <v>0.36499999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A3" r:id="rId2"/>
+    <hyperlink ref="A4" r:id="rId3"/>
+    <hyperlink ref="A5" r:id="rId4"/>
+    <hyperlink ref="A6" r:id="rId5"/>
+    <hyperlink ref="A7" r:id="rId6"/>
+    <hyperlink ref="A8" r:id="rId7"/>
+    <hyperlink ref="A9" r:id="rId8"/>
+    <hyperlink ref="A10" r:id="rId9"/>
+    <hyperlink ref="A11" r:id="rId10"/>
+    <hyperlink ref="A12" r:id="rId11"/>
+    <hyperlink ref="A13" r:id="rId12"/>
+    <hyperlink ref="A14" r:id="rId13"/>
+    <hyperlink ref="A15" r:id="rId14"/>
+    <hyperlink ref="A16" r:id="rId15"/>
+    <hyperlink ref="A17" r:id="rId16"/>
+    <hyperlink ref="A18" r:id="rId17"/>
+    <hyperlink ref="A19" r:id="rId18"/>
+    <hyperlink ref="A20" r:id="rId19"/>
+    <hyperlink ref="A21" r:id="rId20"/>
+    <hyperlink ref="A22" r:id="rId21"/>
+    <hyperlink ref="A23" r:id="rId22"/>
+    <hyperlink ref="A24" r:id="rId23"/>
+    <hyperlink ref="A25" r:id="rId24"/>
+    <hyperlink ref="A26" r:id="rId25"/>
+    <hyperlink ref="A27" r:id="rId26"/>
+    <hyperlink ref="A28" r:id="rId27"/>
+    <hyperlink ref="A29" r:id="rId28"/>
+    <hyperlink ref="A30" r:id="rId29"/>
+    <hyperlink ref="A31" r:id="rId30"/>
+    <hyperlink ref="A32" r:id="rId31"/>
+    <hyperlink ref="A33" r:id="rId32"/>
+    <hyperlink ref="A34" r:id="rId33"/>
+    <hyperlink ref="A35" r:id="rId34"/>
+    <hyperlink ref="A36" r:id="rId35"/>
+    <hyperlink ref="A37" r:id="rId36"/>
+    <hyperlink ref="A38" r:id="rId37"/>
+    <hyperlink ref="A39" r:id="rId38"/>
+    <hyperlink ref="A40" r:id="rId39"/>
+    <hyperlink ref="A41" r:id="rId40"/>
+    <hyperlink ref="A42" r:id="rId41"/>
+    <hyperlink ref="A43" r:id="rId42"/>
+    <hyperlink ref="A44" r:id="rId43"/>
+    <hyperlink ref="A45" r:id="rId44"/>
+    <hyperlink ref="A46" r:id="rId45"/>
+    <hyperlink ref="A47" r:id="rId46"/>
+    <hyperlink ref="A48" r:id="rId47"/>
+    <hyperlink ref="A49" r:id="rId48"/>
+    <hyperlink ref="A50" r:id="rId49"/>
+    <hyperlink ref="A51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>